--- a/Comparison Table of k and p Values (root at local minimum).xlsx
+++ b/Comparison Table of k and p Values (root at local minimum).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olincollege-my.sharepoint.com/personal/mepstein_olin_edu/Documents/Desktop/Applied Math/Assignment-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="8_{F5548F79-425C-4B76-B71C-57BD59B12E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{769214D8-DED9-4E5C-9A8B-C42A6936DB22}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="8_{F5548F79-425C-4B76-B71C-57BD59B12E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B2A6AB8-566D-47A6-933F-63D0A35597E6}"/>
   <bookViews>
-    <workbookView xWindow="2652" yWindow="2652" windowWidth="17280" windowHeight="8880" xr2:uid="{D244108E-BDF8-4038-A556-2A9E06F46F59}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D244108E-BDF8-4038-A556-2A9E06F46F59}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Method</t>
   </si>
@@ -56,9 +56,6 @@
     <t>Measured p value</t>
   </si>
   <si>
-    <t>Bisection Method</t>
-  </si>
-  <si>
     <t>Newton's Method</t>
   </si>
   <si>
@@ -66,9 +63,6 @@
   </si>
   <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>Fzero Method</t>
   </si>
   <si>
     <t>Comparison Table of k and p Values (root at local minimum)</t>
@@ -196,6 +190,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -515,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D957BD8-E315-42A5-8A96-E041D4F91664}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
@@ -527,7 +525,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -556,71 +554,33 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2">
-        <v>0.55789999999999995</v>
-      </c>
-      <c r="D3" s="3">
-        <v>1</v>
-      </c>
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="3">
-        <v>0.97570000000000001</v>
+        <v>1.0313000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2">
-        <v>3.73E-2</v>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="C4" s="2">
-        <v>6.9000000000000006E-2</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2</v>
-      </c>
+        <v>0.76639999999999997</v>
+      </c>
+      <c r="D4" s="3"/>
       <c r="E4" s="3">
-        <v>1.9996</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0.19650000000000001</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1.6</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1.6163000000000001</v>
+        <v>1.0297000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2">
-        <v>9.4799999999999995E-2</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1.6091</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C8" s="1"/>
+      <c r="C6" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Comparison Table of k and p Values (root at local minimum).xlsx
+++ b/Comparison Table of k and p Values (root at local minimum).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olincollege-my.sharepoint.com/personal/mepstein_olin_edu/Documents/Desktop/Applied Math/Assignment-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="8_{F5548F79-425C-4B76-B71C-57BD59B12E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B2A6AB8-566D-47A6-933F-63D0A35597E6}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="8_{F5548F79-425C-4B76-B71C-57BD59B12E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7112020F-FEC7-459C-AB62-006F9C349AF2}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D244108E-BDF8-4038-A556-2A9E06F46F59}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Method</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>Comparison Table of k and p Values (root at local minimum)</t>
+  </si>
+  <si>
+    <t>Inf</t>
   </si>
 </sst>
 </file>
@@ -553,13 +556,15 @@
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2">
-        <v>2</v>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="C3" s="2">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="D3" s="3"/>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
       <c r="E3" s="3">
         <v>1.0313000000000001</v>
       </c>
@@ -574,7 +579,9 @@
       <c r="C4" s="2">
         <v>0.76639999999999997</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="3">
+        <v>1.6</v>
+      </c>
       <c r="E4" s="3">
         <v>1.0297000000000001</v>
       </c>
